--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260724_205757.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260724_205757.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260724_205757.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260724_205757.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260724_205757.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260724_205757.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260724_205757.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260724_205757.xlsx
@@ -5666,7 +5666,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8694,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
